--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>3BBLACKBIO</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1072.87</v>
+        <v>1385.38</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1072.85</v>
+        <v>1319.68</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1073.2</v>
+        <v>1447.8</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1073.19</v>
+        <v>1457.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ARCHIDPLY</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>96.3</v>
+        <v>84.87</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>92.77</v>
+        <v>80.55</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>96.18000000000001</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>96.12</v>
+        <v>87.89</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASAHIINDIA</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>950.17</v>
+        <v>16.63</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>917.74</v>
+        <v>15.21</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>957.05</v>
+        <v>17.53</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>954.45</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BLUECHIP</t>
+          <t>ASIANTILES</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1.84</v>
+        <v>48.1</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1.84</v>
+        <v>46.81</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.9</v>
+        <v>49.61</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.9</v>
+        <v>49.63</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>CASHIETF</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1075.56</v>
+        <v>1564.6</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1075.54</v>
+        <v>1499.06</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1075.87</v>
+        <v>1717.7</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1075.87</v>
+        <v>1717.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>COUNCODOS</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>6.72</v>
+        <v>585.21</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>6.43</v>
+        <v>559</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>6.99</v>
+        <v>616.75</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>7</v>
+        <v>617.35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>DALMIASUG</t>
+          <t>BLUECHIP</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>458.46</v>
+        <v>2.1</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>429.42</v>
+        <v>2.1</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>475.55</v>
+        <v>2.18</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>472.35</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DHAMPURSUG</t>
+          <t>BROOKS</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>174.07</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>163.31</v>
+        <v>63.24</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>176.18</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>176.85</v>
+        <v>67.73999999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CARERATING</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>13.99</v>
+        <v>1684.4</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>13.99</v>
+        <v>1628.06</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>15.38</v>
+        <v>1729</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>15.38</v>
+        <v>1734.9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DUCON</t>
+          <t>CARRARO</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3.32</v>
+        <v>552.5599999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3.13</v>
+        <v>536.76</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3.4</v>
+        <v>559.4</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>3.46</v>
+        <v>558</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DWARKESH</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>46.1</v>
+        <v>4682.58</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>43.16</v>
+        <v>4556.22</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>48.28</v>
+        <v>4821.8</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>48.6</v>
+        <v>4810</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1043.9</v>
+        <v>1082.1</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1043.88</v>
+        <v>1006.34</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1044.21</v>
+        <v>1174.8</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1044.21</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>EQUIPPP</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>22.23</v>
+        <v>9134.9</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>21.12</v>
+        <v>8890.700000000001</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>23.39</v>
+        <v>9467</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>23.4</v>
+        <v>9467</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.79</v>
+        <v>17.62</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>0.78</v>
+        <v>17.62</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.83</v>
+        <v>18.31</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.84</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>149.22</v>
+        <v>470.12</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>139.88</v>
+        <v>445.95</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>157.25</v>
+        <v>493.2</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>156.99</v>
+        <v>490.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GLAXO</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>2811.58</v>
+        <v>1976.94</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>2691.3</v>
+        <v>1897.88</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>3032.4</v>
+        <v>1976.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>3025.2</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GOODLUCK</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1337.8</v>
+        <v>81.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1290.32</v>
+        <v>77.72</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1363.3</v>
+        <v>83.44</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1354.8</v>
+        <v>83.09999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GPPL</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>162.28</v>
+        <v>43.62</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>156.78</v>
+        <v>42.24</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>165.13</v>
+        <v>44.69</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>165.1</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GSLSU</t>
+          <t>FRACTAL</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>33.92</v>
+        <v>849.71</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>32.23</v>
+        <v>827.27</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>36.61</v>
+        <v>852.15</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>36.24</v>
+        <v>844</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>GATECH</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>2199.86</v>
+        <v>1.04</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>2109.5</v>
+        <v>1.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>2307.9</v>
+        <v>1.1</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>2311</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HARSHA</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>429.86</v>
+        <v>2295.98</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>414.62</v>
+        <v>2205.04</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>436.55</v>
+        <v>2412</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>435.5</v>
+        <v>2419.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>HNDFDS</t>
+          <t>IOLCP</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>626.37</v>
+        <v>190.95</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>601.54</v>
+        <v>181.28</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>643.25</v>
+        <v>193.69</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>645.5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>INDOTECH</t>
+          <t>JTLIND</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>3692.04</v>
+        <v>86.16</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>3511.04</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>3709.8</v>
+        <v>89.93000000000001</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>3710</v>
+        <v>89.33</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>INDOUS</t>
+          <t>KHADIM</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>86.56999999999999</v>
+        <v>114.17</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>80.56999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>86.86</v>
+        <v>116.16</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>87.40000000000001</v>
+        <v>116.16</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LCL</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>559</v>
+        <v>1005.72</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>531.97</v>
+        <v>1005.7</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>561.3</v>
+        <v>1006.32</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>556</v>
+        <v>1006.32</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1051.91</v>
+        <v>118.82</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1051.89</v>
+        <v>115.42</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1052.2</v>
+        <v>122.62</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1052.2</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>MAZDA</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1004.24</v>
+        <v>248.19</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1004.23</v>
+        <v>240</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1004.76</v>
+        <v>251.82</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1004.76</v>
+        <v>251.1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>MOREPENLAB</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1094.87</v>
+        <v>102.01</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1094.82</v>
+        <v>95.97</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1095.2</v>
+        <v>107.16</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1095.21</v>
+        <v>107.38</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>115.51</v>
+        <v>27.49</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>115.49</v>
+        <v>26.63</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>115.53</v>
+        <v>28.04</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>115.54</v>
+        <v>28.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>NATCAPSUQ</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1117.58</v>
+        <v>203.16</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1117.56</v>
+        <v>184.51</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1117.89</v>
+        <v>212.38</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1117.89</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>MAHASTEEL</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1099.5</v>
+        <v>1.43</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1047.7</v>
+        <v>1.42</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1140.7</v>
+        <v>1.47</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1140</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>MANINDS</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>629.41</v>
+        <v>20.29</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>603.24</v>
+        <v>19.28</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>643.05</v>
+        <v>21.49</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>643</v>
+        <v>20.91</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>MANIPALHOS</t>
+          <t>RATNAVEER</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>727.46</v>
+        <v>296.21</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>699.91</v>
+        <v>278.35</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>744.8</v>
+        <v>306.02</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>743</v>
+        <v>305.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>MAWANASUG</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>126.91</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>118.49</v>
+        <v>9.31</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>128.72</v>
+        <v>10.32</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>128.48</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>RPEL</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>478.69</v>
+        <v>1758.58</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>449.33</v>
+        <v>1664.96</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>490.15</v>
+        <v>1771.2</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>493</v>
+        <v>1790.2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MODISONLTD</t>
+          <t>SETL</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>357.18</v>
+        <v>349.26</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>347.73</v>
+        <v>331.3</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>392.35</v>
+        <v>369.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>390.1</v>
+        <v>368.5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MONTECARLO</t>
+          <t>SHIVALIK</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>528.35</v>
+        <v>301.29</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>514.83</v>
+        <v>283.42</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>545.45</v>
+        <v>322.19</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>546</v>
+        <v>322.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MSTCLTD</t>
+          <t>SOMANYCERA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>662.29</v>
+        <v>566.39</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>625.75</v>
+        <v>547.73</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>703.75</v>
+        <v>557.3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>701.5</v>
+        <v>562.9</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>NITINSPIN</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>578.74</v>
+        <v>705.83</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>547.83</v>
+        <v>679.24</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>583.55</v>
+        <v>728.45</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>584.95</v>
+        <v>730</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>OCCLLTD</t>
+          <t>SUDARSCHEM</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>160.79</v>
+        <v>1259.76</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>153.85</v>
+        <v>1225.58</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>165.14</v>
+        <v>1266.8</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>166.95</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>125.01</v>
+        <v>14.76</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>118.01</v>
+        <v>14.76</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>130.13</v>
+        <v>15.34</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>130</v>
+        <v>15.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SAMBHV</t>
+          <t>VINCOFE</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,248 +1711,16 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>123.54</v>
+        <v>176.38</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>118.76</v>
+        <v>167.03</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>122.91</v>
+        <v>185.77</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>1052.07</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>1051.99</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>1052.4</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>1052.4</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>SONAMLTD</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>60.22</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>56.04</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>67.19</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>UTLSOLAR</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>457.15</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>430.33</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>483.95</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>482.4</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>UTTAMSUGAR</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>287.72</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>268.45</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>300.99</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>300.99</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>VCL</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>1.94</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>VIJIFIN</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>12.64</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>13.13</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>13.13</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>VIPULLTD</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>14.59</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>15.16</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>15.16</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>ZENTEC</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>1938.98</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>1856.66</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>1932.6</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>1931.3</v>
+        <v>185.94</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1385.38</v>
+        <v>1438.94</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1319.68</v>
+        <v>1363.88</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1447.8</v>
+        <v>1523.5</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1457.9</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>84.87</v>
+        <v>17.1</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>80.55</v>
+        <v>15.83</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>88.20999999999999</v>
+        <v>17.49</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>87.89</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>16.63</v>
+        <v>1074.65</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>15.21</v>
+        <v>1074.63</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>17.53</v>
+        <v>1075.03</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>17.5</v>
+        <v>1075.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ASIANTILES</t>
+          <t>ATHERENERG</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>48.1</v>
+        <v>1619.86</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>46.81</v>
+        <v>1547.38</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>49.61</v>
+        <v>1725.6</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>49.63</v>
+        <v>1725.6</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>BENGALASM</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>1564.6</v>
+        <v>6420.8</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>1499.06</v>
+        <v>6243.2</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1717.7</v>
+        <v>6661.5</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1717.7</v>
+        <v>6699.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>585.21</v>
+        <v>242.55</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>559</v>
+        <v>234.8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>616.75</v>
+        <v>263.2</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>617.35</v>
+        <v>263.2</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BLUECHIP</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>2.1</v>
+        <v>598.3099999999999</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>2.1</v>
+        <v>569.84</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>2.18</v>
+        <v>630.4</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.18</v>
+        <v>631</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BROOKS</t>
+          <t>BODALCHEM</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>66.43000000000001</v>
+        <v>107</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>63.24</v>
+        <v>97.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>66.54000000000001</v>
+        <v>126.76</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>67.73999999999999</v>
+        <v>128.1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CARERATING</t>
+          <t>CMRGREEN</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1684.4</v>
+        <v>227.27</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1628.06</v>
+        <v>219.36</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1729</v>
+        <v>231.03</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1734.9</v>
+        <v>231.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CARRARO</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>552.5599999999999</v>
+        <v>4750.38</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>536.76</v>
+        <v>4620.84</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>559.4</v>
+        <v>4829.5</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>558</v>
+        <v>4761.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>CYIENT</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4682.58</v>
+        <v>1128.1</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>4556.22</v>
+        <v>1055.71</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4821.8</v>
+        <v>1164.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4810</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1082.1</v>
+        <v>17.96</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1006.34</v>
+        <v>17.96</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1174.8</v>
+        <v>18.67</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1175</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DYCL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>9134.9</v>
+        <v>495.14</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>8890.700000000001</v>
+        <v>458.17</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>9467</v>
+        <v>542.4</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>9467</v>
+        <v>543</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>ELECTCAST</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>17.62</v>
+        <v>83</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>17.62</v>
+        <v>79.48</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>18.31</v>
+        <v>83.83</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>18.31</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>FEDDERSHOL</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>470.12</v>
+        <v>44.7</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>445.95</v>
+        <v>43.47</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>493.2</v>
+        <v>45.21</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>490.9</v>
+        <v>45.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>FINEORG</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1976.94</v>
+        <v>5309.36</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1897.88</v>
+        <v>5163.7</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1976.9</v>
+        <v>5255.5</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1956</v>
+        <v>5227</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>81.2</v>
+        <v>26.27</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>77.72</v>
+        <v>23.88</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>83.44</v>
+        <v>29.09</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>83.09999999999999</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>HAPPYFORGE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>43.62</v>
+        <v>2348.18</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>42.24</v>
+        <v>2246.98</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>44.69</v>
+        <v>2420.4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>FRACTAL</t>
+          <t>HDFCLIQUID</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>849.71</v>
+        <v>1075.76</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>827.27</v>
+        <v>1075.73</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>852.15</v>
+        <v>1076.13</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>844</v>
+        <v>1076.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GATECH</t>
+          <t>JINDWORLD</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1.04</v>
+        <v>39.14</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.03</v>
+        <v>36.81</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1.1</v>
+        <v>42.08</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1.11</v>
+        <v>41.98</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>LIQGRWBEES</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2295.98</v>
+        <v>1053.55</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2205.04</v>
+        <v>1053.51</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2412</v>
+        <v>1053.9</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>2419.1</v>
+        <v>1053.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>IOLCP</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>190.95</v>
+        <v>1005.95</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>181.28</v>
+        <v>1005.94</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>193.69</v>
+        <v>1006.46</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>194</v>
+        <v>1006.46</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>JTLIND</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>86.16</v>
+        <v>1096.64</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>81.98999999999999</v>
+        <v>1096.62</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>89.93000000000001</v>
+        <v>1097.02</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>89.33</v>
+        <v>1097.03</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>KHADIM</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>114.17</v>
+        <v>115.7</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>108.7</v>
+        <v>115.68</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>116.16</v>
+        <v>115.73</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>116.16</v>
+        <v>115.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1005.72</v>
+        <v>1119.33</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1005.7</v>
+        <v>1119.31</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1006.32</v>
+        <v>1119.72</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1006.32</v>
+        <v>1119.72</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>MANINFRA</t>
+          <t>MAFANG</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>118.82</v>
+        <v>208.1</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>115.42</v>
+        <v>207.85</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>122.62</v>
+        <v>211.05</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>122</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>MAZDA</t>
+          <t>MANINFRA</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>248.19</v>
+        <v>121.22</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>240</v>
+        <v>117.3</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>251.82</v>
+        <v>124.56</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>251.1</v>
+        <v>123.75</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MOREPENLAB</t>
+          <t>MOTOGENFIN</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>102.01</v>
+        <v>27.92</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>95.97</v>
+        <v>26.89</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>107.16</v>
+        <v>28.03</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>107.38</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MOTOGENFIN</t>
+          <t>NOIDATOLL</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>27.49</v>
+        <v>4.28</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>26.63</v>
+        <v>4.08</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>28.04</v>
+        <v>4.23</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>28.1</v>
+        <v>4.25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NATCAPSUQ</t>
+          <t>NURECA</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,16 +1363,16 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>203.16</v>
+        <v>330.29</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>184.51</v>
+        <v>313.03</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>212.38</v>
+        <v>339</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>211</v>
+        <v>338.2</v>
       </c>
     </row>
     <row r="32">
@@ -1392,16 +1392,16 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="33">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>20.29</v>
+        <v>21.47</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>19.28</v>
+        <v>19.74</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>21.49</v>
+        <v>24.44</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>20.91</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>RATNAVEER</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>296.21</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>278.35</v>
+        <v>9.77</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>306.02</v>
+        <v>10.83</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>305.8</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>RSL</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>9.390000000000001</v>
+        <v>177.45</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>9.31</v>
+        <v>170.08</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>10.32</v>
+        <v>176.74</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>10.32</v>
+        <v>177.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RPEL</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1758.58</v>
+        <v>1053.81</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1664.96</v>
+        <v>1053.79</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>1771.2</v>
+        <v>1054.18</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>1790.2</v>
+        <v>1054.17</v>
       </c>
     </row>
     <row r="37">
@@ -1537,16 +1537,16 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>349.26</v>
+        <v>362.38</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>331.3</v>
+        <v>346.9</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>369.5</v>
+        <v>387.05</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>368.5</v>
+        <v>387.95</v>
       </c>
     </row>
     <row r="38">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>301.29</v>
+        <v>311.97</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>283.42</v>
+        <v>296.21</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>322.19</v>
+        <v>338.05</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>322.19</v>
+        <v>336</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SOMANYCERA</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,132 +1595,16 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>566.39</v>
+        <v>15.05</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>547.73</v>
+        <v>15.05</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>557.3</v>
+        <v>15.64</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>562.9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>705.83</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>679.24</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>728.45</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>SUDARSCHEM</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>1259.76</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>1225.58</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>1266.8</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>VIJIFIN</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>14.76</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>15.34</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>VINCOFE</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>176.38</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>167.03</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>185.77</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>185.94</v>
+        <v>15.64</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1438.94</v>
+        <v>1494.12</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1363.88</v>
+        <v>1404.44</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1523.5</v>
+        <v>1478.6</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1525</v>
+        <v>1478.9</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>AARTIPHARM</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,16 +551,16 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17.1</v>
+        <v>862.21</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15.83</v>
+        <v>830.0700000000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.49</v>
+        <v>867.25</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>17.57</v>
+        <v>864.45</v>
       </c>
     </row>
     <row r="4">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1074.65</v>
+        <v>1074.85</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1074.63</v>
+        <v>1074.83</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1075.03</v>
+        <v>1075.16</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1075.04</v>
+        <v>1075.18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ATHERENERG</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1619.86</v>
+        <v>615.12</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1547.38</v>
+        <v>582.04</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1725.6</v>
+        <v>648.65</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1725.6</v>
+        <v>649.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BENGALASM</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>6420.8</v>
+        <v>18.32</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>6243.2</v>
+        <v>18.32</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>6661.5</v>
+        <v>19.04</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>6699.5</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>ELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>242.55</v>
+        <v>1046.84</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>234.8</v>
+        <v>1044.46</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>263.2</v>
+        <v>1046.13</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>263.2</v>
+        <v>1046.12</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>GEEKAYWIRE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>598.3099999999999</v>
+        <v>27.84</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>569.84</v>
+        <v>24.89</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>630.4</v>
+        <v>27.86</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>631</v>
+        <v>28.2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BODALCHEM</t>
+          <t>GHCLTEXTIL</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>107</v>
+        <v>137.12</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>97.86</v>
+        <v>130.75</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>126.76</v>
+        <v>139.35</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>128.1</v>
+        <v>139.94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CMRGREEN</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>227.27</v>
+        <v>164.84</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>219.36</v>
+        <v>155.76</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>231.03</v>
+        <v>168.3</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>231.15</v>
+        <v>168.05</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CRISIL</t>
+          <t>KALYANIFRG</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>4750.38</v>
+        <v>937.4400000000001</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>4620.84</v>
+        <v>805.97</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4829.5</v>
+        <v>1113.65</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4761.5</v>
+        <v>1176.6</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CYIENT</t>
+          <t>KANANIIND</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1128.1</v>
+        <v>1.56</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1055.71</v>
+        <v>1.47</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1164.6</v>
+        <v>1.53</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1153</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>17.96</v>
+        <v>1006.18</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>17.96</v>
+        <v>1006.17</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>18.67</v>
+        <v>1006.57</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>18.67</v>
+        <v>1006.57</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DYCL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>495.14</v>
+        <v>1096.83</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>458.17</v>
+        <v>1096.81</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>542.4</v>
+        <v>1097.15</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>543</v>
+        <v>1097.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ELECTCAST</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>83</v>
+        <v>115.72</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>79.48</v>
+        <v>115.7</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>83.83</v>
+        <v>115.74</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>83.8</v>
+        <v>115.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>FEDDERSHOL</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>44.7</v>
+        <v>1119.52</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>43.47</v>
+        <v>1119.5</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>45.21</v>
+        <v>1119.83</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45.15</v>
+        <v>1119.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>FINEORG</t>
+          <t>MALLCOM</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>5309.36</v>
+        <v>1022.78</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>5163.7</v>
+        <v>971.35</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>5255.5</v>
+        <v>1021.15</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>5227</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>NIRAJISPAT</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>26.27</v>
+        <v>345.65</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>23.88</v>
+        <v>333.61</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>29.09</v>
+        <v>429.65</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>29.11</v>
+        <v>429.65</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HAPPYFORGE</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>2348.18</v>
+        <v>1.47</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>2246.98</v>
+        <v>1.47</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>2420.4</v>
+        <v>1.51</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>2424</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>HDFCLIQUID</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1075.76</v>
+        <v>22.76</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1075.73</v>
+        <v>20.89</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1076.13</v>
+        <v>24.86</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1076.12</v>
+        <v>24.95</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>JINDWORLD</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>39.14</v>
+        <v>22364.6</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>36.81</v>
+        <v>21354.2</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>42.08</v>
+        <v>22715</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>41.98</v>
+        <v>22865</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>LIQGRWBEES</t>
+          <t>RNBDENIMS</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1053.55</v>
+        <v>10.34</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1053.51</v>
+        <v>10.26</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1053.9</v>
+        <v>11.37</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1053.91</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1005.95</v>
+        <v>1054</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1005.94</v>
+        <v>1053.98</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1006.46</v>
+        <v>1054.3</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1006.46</v>
+        <v>1054.32</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>SUPERSPIN</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1096.64</v>
+        <v>6.42</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1096.62</v>
+        <v>6.15</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1097.02</v>
+        <v>6.51</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1097.03</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>UDS</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>115.7</v>
+        <v>227.69</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>115.68</v>
+        <v>221.42</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>115.73</v>
+        <v>231.44</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>115.73</v>
+        <v>233.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>VIJIFIN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,393 +1218,16 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1119.33</v>
+        <v>15.34</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1119.31</v>
+        <v>15.34</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1119.72</v>
+        <v>15.95</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1119.72</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>MAFANG</t>
-        </is>
-      </c>
-      <c r="B27" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>208.1</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>207.85</v>
-      </c>
-      <c r="F27" s="3" t="n">
-        <v>211.05</v>
-      </c>
-      <c r="G27" s="3" t="n">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>MANINFRA</t>
-        </is>
-      </c>
-      <c r="B28" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>121.22</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>117.3</v>
-      </c>
-      <c r="F28" s="3" t="n">
-        <v>124.56</v>
-      </c>
-      <c r="G28" s="3" t="n">
-        <v>123.75</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>MOTOGENFIN</t>
-        </is>
-      </c>
-      <c r="B29" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>26.89</v>
-      </c>
-      <c r="F29" s="3" t="n">
-        <v>28.03</v>
-      </c>
-      <c r="G29" s="3" t="n">
-        <v>27.5</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>NOIDATOLL</t>
-        </is>
-      </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>NURECA</t>
-        </is>
-      </c>
-      <c r="B31" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v>330.29</v>
-      </c>
-      <c r="E31" s="3" t="n">
-        <v>313.03</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>339</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>338.2</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>PARSVNATH</t>
-        </is>
-      </c>
-      <c r="B32" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>1.49</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>PRAENG</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v>21.47</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>19.74</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>24.44</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>24.34</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>RNBDENIMS</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>10.83</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>10.83</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>177.45</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>170.08</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>176.74</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>177.5</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>1053.81</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>1053.79</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>1054.18</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>1054.17</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SETL</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>362.38</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>346.9</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>387.05</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>387.95</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SHIVALIK</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>311.97</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>296.21</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>338.05</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>VIJIFIN</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>15.64</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>15.64</v>
+        <v>15.95</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>3BBLACKBIO</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1494.12</v>
+        <v>1075.04</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1404.44</v>
+        <v>1075.02</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1478.6</v>
+        <v>1075.29</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1478.9</v>
+        <v>1075.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AARTIPHARM</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>862.21</v>
+        <v>153.96</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>830.0700000000001</v>
+        <v>147.58</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>867.25</v>
+        <v>159.95</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>864.45</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1074.85</v>
+        <v>606.35</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>1074.83</v>
+        <v>589.59</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1075.16</v>
+        <v>600.4</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1075.18</v>
+        <v>599.55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>615.12</v>
+        <v>1695.12</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>582.04</v>
+        <v>1621.76</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>648.65</v>
+        <v>1730.4</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>649.9</v>
+        <v>1727.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>AYMSYNTEX</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>18.32</v>
+        <v>300.39</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>18.32</v>
+        <v>271.69</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19.04</v>
+        <v>317.25</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>19.04</v>
+        <v>317.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ELIQUID</t>
+          <t>BLISSGVS</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1046.84</v>
+        <v>632.92</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1044.46</v>
+        <v>598</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1046.13</v>
+        <v>639.35</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1046.12</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GEEKAYWIRE</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>27.84</v>
+        <v>20.41</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>24.89</v>
+        <v>18.57</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>27.86</v>
+        <v>23.88</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>28.2</v>
+        <v>23.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GHCLTEXTIL</t>
+          <t>DRAGARWQ</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>137.12</v>
+        <v>5376.9</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>130.75</v>
+        <v>5247.9</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>139.35</v>
+        <v>5339</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>139.94</v>
+        <v>5305.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>164.84</v>
+        <v>18.68</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>155.76</v>
+        <v>18.68</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>168.3</v>
+        <v>19.42</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>168.05</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>KALYANIFRG</t>
+          <t>GKSL</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>937.4400000000001</v>
+        <v>168.72</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>805.97</v>
+        <v>159.41</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1113.65</v>
+        <v>171.51</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1176.6</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>KANANIIND</t>
+          <t>GYFTR</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,16 +812,16 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1.56</v>
+        <v>183.23</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>1.47</v>
+        <v>170.22</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.53</v>
+        <v>180.23</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.54</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13">
@@ -841,16 +841,16 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1006.18</v>
+        <v>1006.38</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1006.17</v>
+        <v>1006.36</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1006.57</v>
+        <v>1006.7</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1006.57</v>
+        <v>1006.7</v>
       </c>
     </row>
     <row r="14">
@@ -870,16 +870,16 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1096.83</v>
+        <v>1097.02</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1096.81</v>
+        <v>1097</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1097.15</v>
+        <v>1097.27</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1097.15</v>
+        <v>1097.27</v>
       </c>
     </row>
     <row r="15">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
+        <v>115.74</v>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>115.72</v>
       </c>
-      <c r="E15" s="3" t="n">
-        <v>115.7</v>
-      </c>
       <c r="F15" s="3" t="n">
-        <v>115.74</v>
+        <v>115.76</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>115.74</v>
+        <v>115.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1119.52</v>
+        <v>1101.38</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1119.5</v>
+        <v>1101.31</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1119.83</v>
+        <v>1101.63</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1119.83</v>
+        <v>1101.62</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>MALLCOM</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1022.78</v>
+        <v>1119.71</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>971.35</v>
+        <v>1119.69</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1021.15</v>
+        <v>1119.96</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1020</v>
+        <v>1119.97</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>NIRAJISPAT</t>
+          <t>PAR</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,16 +986,16 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>345.65</v>
+        <v>142.09</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>333.61</v>
+        <v>123.78</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>429.65</v>
+        <v>164.95</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>429.65</v>
+        <v>163.3</v>
       </c>
     </row>
     <row r="19">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>PLAZACABLE</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>22.76</v>
+        <v>59.23</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>20.89</v>
+        <v>55.35</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>24.86</v>
+        <v>62.62</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>24.95</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>PRAENG</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>22364.6</v>
+        <v>24.09</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>21354.2</v>
+        <v>22.03</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>22715</v>
+        <v>25.75</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>22865</v>
+        <v>25.84</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>RNBDENIMS</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>10.34</v>
+        <v>46.4</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>10.26</v>
+        <v>44.09</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>11.37</v>
+        <v>46.42</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>11.37</v>
+        <v>46.89</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1054</v>
+        <v>22987</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1053.98</v>
+        <v>21778.4</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1054.3</v>
+        <v>23820</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>1054.32</v>
+        <v>23635</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SUPERSPIN</t>
+          <t>SAHLIBHFI</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>6.42</v>
+        <v>84.92</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>6.15</v>
+        <v>77.2</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>6.51</v>
+        <v>89.12</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>6.5</v>
+        <v>90.98999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,45 +1189,161 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>227.69</v>
+        <v>1054.19</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>221.42</v>
+        <v>1054.17</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>231.44</v>
+        <v>1054.43</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>233.3</v>
+        <v>1054.43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>1246.49</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>1181.15</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>1292.8</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>TNPETRO</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>130.94</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>121.37</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>137.81</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>136.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>230.75</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>223.88</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>236.61</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>238.71</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
           <t>VIJIFIN</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>15.34</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>15.95</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>15.95</v>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>15.65</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>16.26</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>16.26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>WELENT</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>721.45</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>686.48</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>764.75</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>759</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1075.04</v>
+        <v>5.65</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1075.02</v>
+        <v>5.3</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1075.29</v>
+        <v>7.22</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1075.29</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>153.96</v>
+        <v>1075.23</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>147.58</v>
+        <v>1075.21</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>159.95</v>
+        <v>1075.67</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>160</v>
+        <v>1075.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>606.35</v>
+        <v>765.95</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>589.59</v>
+        <v>732.6900000000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>600.4</v>
+        <v>814.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>599.55</v>
+        <v>816</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>ASIANENE</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1695.12</v>
+        <v>511.81</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>1621.76</v>
+        <v>485.17</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1730.4</v>
+        <v>517.45</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1727.2</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AYMSYNTEX</t>
+          <t>AUSOMENT</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>300.39</v>
+        <v>157.5</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>271.69</v>
+        <v>149.69</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>317.25</v>
+        <v>161.79</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>317.9</v>
+        <v>160.45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BLISSGVS</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>632.92</v>
+        <v>1719.12</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>598</v>
+        <v>1645.9</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>639.35</v>
+        <v>1711.6</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>637</v>
+        <v>1710.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>BIRLACABLE</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>20.41</v>
+        <v>342.4</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>18.57</v>
+        <v>331.76</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>23.88</v>
+        <v>376.55</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>23.88</v>
+        <v>376.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>DRAGARWQ</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>5376.9</v>
+        <v>112.22</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>5247.9</v>
+        <v>106.14</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5339</v>
+        <v>112.84</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>5305.5</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>18.68</v>
+        <v>22.31</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>18.68</v>
+        <v>19.44</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>19.42</v>
+        <v>26.4</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>19.42</v>
+        <v>26.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GKSL</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>168.72</v>
+        <v>641.8099999999999</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>159.41</v>
+        <v>609.9299999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>171.51</v>
+        <v>658.25</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>171.99</v>
+        <v>659</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>GYFTR</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>183.23</v>
+        <v>18.68</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>170.22</v>
+        <v>18.68</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>180.23</v>
+        <v>19.42</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>180</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1006.38</v>
+        <v>578.15</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>1006.36</v>
+        <v>558.74</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1006.7</v>
+        <v>595.15</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1006.7</v>
+        <v>595.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>GLOBAL</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1097.02</v>
+        <v>118.02</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1097</v>
+        <v>110</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1097.27</v>
+        <v>120.45</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1097.27</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>GROWWLIQID</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>115.74</v>
+        <v>110.6</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>115.72</v>
+        <v>110.59</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>115.76</v>
+        <v>110.64</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>115.77</v>
+        <v>110.65</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1101.38</v>
+        <v>1143.08</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1101.31</v>
+        <v>1143.02</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1101.63</v>
+        <v>1143.51</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1101.62</v>
+        <v>1143.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>LIQUIDBETA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1119.71</v>
+        <v>1006.63</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1119.69</v>
+        <v>1006.61</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1119.96</v>
+        <v>1007.04</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1119.97</v>
+        <v>1007.04</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>PAR</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>142.09</v>
+        <v>1097.2</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>123.78</v>
+        <v>1097.18</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>164.95</v>
+        <v>1097.63</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>163.3</v>
+        <v>1097.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1.49</v>
+        <v>115.76</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.49</v>
+        <v>115.74</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.54</v>
+        <v>115.8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1.54</v>
+        <v>115.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>PLAZACABLE</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>59.23</v>
+        <v>1101.56</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>55.35</v>
+        <v>1101.48</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>62.62</v>
+        <v>1102.01</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>62</v>
+        <v>1102.03</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>PRAENG</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>24.09</v>
+        <v>1119.89</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>22.03</v>
+        <v>1119.87</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>25.75</v>
+        <v>1120.33</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>25.84</v>
+        <v>1120.33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>46.4</v>
+        <v>1.52</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>44.09</v>
+        <v>1.52</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>46.42</v>
+        <v>1.57</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>46.89</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>PASUPTAC</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>22987</v>
+        <v>65.55</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>21778.4</v>
+        <v>62.72</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>23820</v>
+        <v>67.64</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>23635</v>
+        <v>67.65000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>SAHLIBHFI</t>
+          <t>PROZONER</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>84.92</v>
+        <v>47.49</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>77.2</v>
+        <v>44.62</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>89.12</v>
+        <v>49.76</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>90.98999999999999</v>
+        <v>49.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1054.19</v>
+        <v>23369</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1054.17</v>
+        <v>22336</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1054.43</v>
+        <v>23830</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1054.43</v>
+        <v>23680</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1246.49</v>
+        <v>1054.37</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1181.15</v>
+        <v>1054.35</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1292.8</v>
+        <v>1054.81</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1292</v>
+        <v>1054.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TNPETRO</t>
+          <t>SUDEEPPHRM</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>130.94</v>
+        <v>1283.64</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>121.37</v>
+        <v>1219.95</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>137.81</v>
+        <v>1329.3</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>136.5</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>TBZ</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>230.75</v>
+        <v>408.93</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>223.88</v>
+        <v>368.62</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>236.61</v>
+        <v>480.85</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>238.71</v>
+        <v>480.85</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>TIJARIA</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,45 +1305,103 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>15.65</v>
+        <v>8.07</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>15.65</v>
+        <v>7.11</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>16.26</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>16.26</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>UDS</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>233.88</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>226</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>239.03</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>238.35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>VIJIFIN</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>16.58</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>16.58</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
           <t>WELENT</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v>721.45</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>686.48</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>764.75</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>759</v>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>749.3</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>705.64</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>813.6</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>818</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G32"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>5.65</v>
+        <v>95.42</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>5.3</v>
+        <v>91.39</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>7.22</v>
+        <v>97.31</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>7.22</v>
+        <v>95.88</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>AEPL</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1075.23</v>
+        <v>17.19</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>1075.21</v>
+        <v>15.65</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1075.67</v>
+        <v>18.02</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1075.67</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>AEROPLANE</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>765.95</v>
+        <v>189.57</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>732.6900000000001</v>
+        <v>180.77</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>814.1</v>
+        <v>198.03</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>816</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ASIANENE</t>
+          <t>AKI</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>511.81</v>
+        <v>6.39</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>485.17</v>
+        <v>6.1</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>517.45</v>
+        <v>7.94</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>519</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AUSOMENT</t>
+          <t>ALPHAGEO</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>157.5</v>
+        <v>314.09</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>149.69</v>
+        <v>299.77</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>161.79</v>
+        <v>324.55</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>160.45</v>
+        <v>319</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1719.12</v>
+        <v>1075.41</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1645.9</v>
+        <v>1075.39</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1711.6</v>
+        <v>1075.79</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1710.1</v>
+        <v>1075.79</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BIRLACABLE</t>
+          <t>ARROWGREEN</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>342.4</v>
+        <v>789.95</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>331.76</v>
+        <v>753.73</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>376.55</v>
+        <v>805.1</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>376.55</v>
+        <v>808.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>AXISCADES</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>112.22</v>
+        <v>1740.16</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>106.14</v>
+        <v>1666.4</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>112.84</v>
+        <v>1778</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>114</v>
+        <v>1777</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>BLUESTONE</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>22.31</v>
+        <v>838.86</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>19.44</v>
+        <v>804.49</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>26.4</v>
+        <v>870</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>26.75</v>
+        <v>872</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>641.8099999999999</v>
+        <v>3821.76</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>609.9299999999999</v>
+        <v>3585.88</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>658.25</v>
+        <v>4376.9</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>659</v>
+        <v>4381</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>18.68</v>
+        <v>272.4</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>18.68</v>
+        <v>258.04</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>19.42</v>
+        <v>275.7</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>19.42</v>
+        <v>273.8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>CROWN</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>578.15</v>
+        <v>113.98</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>558.74</v>
+        <v>108.92</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>595.15</v>
+        <v>115.39</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>595.6</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>GLOBAL</t>
+          <t>CYBERMEDIA</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>118.02</v>
+        <v>24.27</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>110</v>
+        <v>21.12</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>120.45</v>
+        <v>26.57</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>121</v>
+        <v>26.52</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>GROWWLIQID</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>110.6</v>
+        <v>658.61</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>110.59</v>
+        <v>624.9299999999999</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>110.64</v>
+        <v>677.05</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>110.65</v>
+        <v>682</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1143.08</v>
+        <v>19.05</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1143.02</v>
+        <v>19.05</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1143.51</v>
+        <v>19.8</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1143.5</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETA</t>
+          <t>GCSL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1006.63</v>
+        <v>588.4</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1006.61</v>
+        <v>571.14</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1007.04</v>
+        <v>601.85</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1007.04</v>
+        <v>602.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>GFLLIMITED</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1097.2</v>
+        <v>61.01</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1097.18</v>
+        <v>57.33</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1097.63</v>
+        <v>62.17</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1097.63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>115.76</v>
+        <v>1215.96</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>115.74</v>
+        <v>1179.16</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>115.8</v>
+        <v>1233.7</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>115.79</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>IONEXCHANG</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1101.56</v>
+        <v>403.46</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1101.48</v>
+        <v>379.06</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1102.01</v>
+        <v>439.1</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1102.03</v>
+        <v>436</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1119.89</v>
+        <v>659.03</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1119.87</v>
+        <v>631.4400000000001</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1120.33</v>
+        <v>664.15</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>1120.33</v>
+        <v>666</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>KEEPLEARN</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1.52</v>
+        <v>2.04</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>PASUPTAC</t>
+          <t>LENSKART</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>65.55</v>
+        <v>684.62</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>62.72</v>
+        <v>666.76</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>67.64</v>
+        <v>688</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>67.65000000000001</v>
+        <v>688.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>47.49</v>
+        <v>1143.3</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>44.62</v>
+        <v>1143.22</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>49.76</v>
+        <v>1143.64</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>49.9</v>
+        <v>1143.63</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>PTCIL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>23369</v>
+        <v>1097.38</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>22336</v>
+        <v>1097.36</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>23830</v>
+        <v>1097.78</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>23680</v>
+        <v>1097.79</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>1054.37</v>
+        <v>115.78</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1054.35</v>
+        <v>115.76</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1054.81</v>
+        <v>115.81</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1054.81</v>
+        <v>115.81</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1283.64</v>
+        <v>1101.74</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1219.95</v>
+        <v>1101.68</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1329.3</v>
+        <v>1102.13</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1335</v>
+        <v>1102.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>408.93</v>
+        <v>1120.06</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>368.62</v>
+        <v>1120.04</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>480.85</v>
+        <v>1120.4</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>480.85</v>
+        <v>1120.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TIJARIA</t>
+          <t>MAHSEAMLES</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>8.07</v>
+        <v>686.87</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.11</v>
+        <v>653.4400000000001</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>688.95</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>9.539999999999999</v>
+        <v>689</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>UDS</t>
+          <t>MONTECARLO</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>233.88</v>
+        <v>564.42</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>226</v>
+        <v>548.54</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>239.03</v>
+        <v>575.45</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>238.35</v>
+        <v>578</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>NCLIND</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>15.95</v>
+        <v>178.18</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>15.95</v>
+        <v>174.12</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>16.58</v>
+        <v>178.3</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>16.58</v>
+        <v>177.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>WELENT</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,16 +1392,596 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>749.3</v>
+        <v>72.12</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>705.64</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>813.6</v>
+        <v>79.41</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>818</v>
+        <v>78.97</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>PROZONER</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>45.41</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>48.01</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>47.82</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>RHETAN</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>23.07</v>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>26.68</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>26.69</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>RKSWAMY</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>93.98</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>91.15000000000001</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>93.66</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>93.11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>RUBYMILLS</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>427.71</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>397.02</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>457</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>44.82</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>43.14</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>46.91</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1054.54</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1054.52</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>1054.91</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>1054.92</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>673.1</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>647.8</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>699.8</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2293.16</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>2170.44</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>2486.8</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>2486.8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>SUDEEPPHRM</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1317.3</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>1252.22</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>1323.3</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>1323.5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>4637.28</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>4553.14</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>4708.3</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>4700</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>SUPRIYA</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>860.48</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>826.41</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>909.1</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>TBZ</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>452.74</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>415.87</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>528.9</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>528.9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>473.47</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>457.91</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>514.9</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>514.9</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>VALIANTORG</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>314.83</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>302.1</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>326.1</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>VIJIFIN</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>16.27</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>16.91</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>VINDHYATEL</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>2803.7</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>2627.48</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>2765</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>2778</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>WHIRLPOOL</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>813.75</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>794.88</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>815.35</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>WINDLAS</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1121.65</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1067.83</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1154.75</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>WOCKPHARMA</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>2025.06</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1923</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>2208</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>2212.8</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G52"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>95.42</v>
+        <v>96.98</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>91.39</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>97.31</v>
+        <v>99.98</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>95.88</v>
+        <v>99.20999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AEPL</t>
+          <t>AIRAN</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>17.19</v>
+        <v>16.06</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15.65</v>
+        <v>15.29</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>18.02</v>
+        <v>17.66</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>17.99</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AEROPLANE</t>
+          <t>ALLCARGO</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>189.57</v>
+        <v>12.76</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>180.77</v>
+        <v>12.16</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>198.03</v>
+        <v>12.75</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>196</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>AKI</t>
+          <t>ALMONDZ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>6.39</v>
+        <v>18.74</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>6.1</v>
+        <v>17.73</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>7.94</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>7.94</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ALPHAGEO</t>
+          <t>AMANTA</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>314.09</v>
+        <v>195.61</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>299.77</v>
+        <v>194.91</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>324.55</v>
+        <v>205.89</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>319</v>
+        <v>205.89</v>
       </c>
     </row>
     <row r="7">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1075.41</v>
+        <v>1075.62</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1075.39</v>
+        <v>1075.59</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1075.79</v>
+        <v>1076.06</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1075.79</v>
+        <v>1076.06</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ARROWGREEN</t>
+          <t>APOLLO</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>789.95</v>
+        <v>401.43</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>753.73</v>
+        <v>388.81</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>805.1</v>
+        <v>422.45</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>808.95</v>
+        <v>420.5</v>
       </c>
     </row>
     <row r="9">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1740.16</v>
+        <v>1791.4</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1666.4</v>
+        <v>1713.52</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1778</v>
+        <v>1875.7</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1777</v>
+        <v>1882.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BLUESTONE</t>
+          <t>BANCOINDIA</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>838.86</v>
+        <v>630.42</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>804.49</v>
+        <v>616.92</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>870</v>
+        <v>635.15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>872</v>
+        <v>634.1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>BGRENERGY</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>3821.76</v>
+        <v>251.52</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3585.88</v>
+        <v>236.85</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>4376.9</v>
+        <v>248.87</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>4381</v>
+        <v>248.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CGCL</t>
+          <t>CENTUM</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>272.4</v>
+        <v>4012.76</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>258.04</v>
+        <v>3746.9</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>275.7</v>
+        <v>4250.5</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>273.8</v>
+        <v>4225.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CROWN</t>
+          <t>DEEDEV</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>113.98</v>
+        <v>676.52</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>108.92</v>
+        <v>642.54</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>115.39</v>
+        <v>674.75</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>115</v>
+        <v>670</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>CYBERMEDIA</t>
+          <t>DEEPINDS</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>24.27</v>
+        <v>774.34</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>21.12</v>
+        <v>730.9</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>26.57</v>
+        <v>792.7</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>26.52</v>
+        <v>794.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>DENTA</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,16 +899,16 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>658.61</v>
+        <v>281.8</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>624.9299999999999</v>
+        <v>271.2</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>677.05</v>
+        <v>283.2</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>682</v>
+        <v>283.55</v>
       </c>
     </row>
     <row r="16">
@@ -943,7 +943,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>GCSL</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>588.4</v>
+        <v>202.48</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>571.14</v>
+        <v>195.51</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>601.85</v>
+        <v>206.06</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>602.7</v>
+        <v>204.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GFLLIMITED</t>
+          <t>GENESYS</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>61.01</v>
+        <v>245.34</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>57.33</v>
+        <v>231.45</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>62.17</v>
+        <v>274.31</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>62</v>
+        <v>272.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1215.96</v>
+        <v>1371.52</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1179.16</v>
+        <v>1337.86</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1233.7</v>
+        <v>1393.4</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1239</v>
+        <v>1391.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>IONEXCHANG</t>
+          <t>GMMPFAUDLR</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>403.46</v>
+        <v>1193.36</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>379.06</v>
+        <v>1123.78</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>439.1</v>
+        <v>1305.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>436</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>659.03</v>
+        <v>396.1</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>631.4400000000001</v>
+        <v>374.79</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>664.15</v>
+        <v>463.5</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>666</v>
+        <v>463.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>KEEPLEARN</t>
+          <t>INDIAGLYCO</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2.04</v>
+        <v>263.86</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.85</v>
+        <v>259.48</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.91</v>
+        <v>301.3</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>1.91</v>
+        <v>301.3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>LENSKART</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>684.62</v>
+        <v>76.58</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>666.76</v>
+        <v>69.44</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>688</v>
+        <v>86.13</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>688.6</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>JASH</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1143.3</v>
+        <v>495.79</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1143.22</v>
+        <v>478.63</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1143.64</v>
+        <v>518.75</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1143.63</v>
+        <v>519.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>JINDRILL</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1097.38</v>
+        <v>672.53</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1097.36</v>
+        <v>643.46</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>1097.78</v>
+        <v>673.75</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>1097.79</v>
+        <v>672.5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>KILITCH</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>115.78</v>
+        <v>181.05</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>115.76</v>
+        <v>173.89</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>115.81</v>
+        <v>188.45</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>115.81</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>KISSHT</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>1101.74</v>
+        <v>318.68</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1101.68</v>
+        <v>303.36</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1102.13</v>
+        <v>322.85</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1102.14</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>KSHINTL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1120.06</v>
+        <v>1081.29</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1120.04</v>
+        <v>1027.03</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1120.4</v>
+        <v>1152.05</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1120.4</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>MAHSEAMLES</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>686.87</v>
+        <v>0.06</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>653.4400000000001</v>
+        <v>0.06</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>688.95</v>
+        <v>0.08</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>689</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>MONTECARLO</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>564.42</v>
+        <v>1143.51</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>548.54</v>
+        <v>1143.42</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>575.45</v>
+        <v>1143.91</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>578</v>
+        <v>1143.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NCLIND</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>178.18</v>
+        <v>1097.58</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>174.12</v>
+        <v>1097.56</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>178.3</v>
+        <v>1098.02</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>177.25</v>
+        <v>1098.02</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>72.12</v>
+        <v>115.8</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>68.29000000000001</v>
+        <v>115.78</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>79.41</v>
+        <v>115.83</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>78.97</v>
+        <v>115.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>LIQUIDPLUS</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1.54</v>
+        <v>1102.14</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1.54</v>
+        <v>1101.89</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.6</v>
+        <v>1102.39</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1.6</v>
+        <v>1102.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PROZONER</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>48.57</v>
+        <v>1120.25</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>45.41</v>
+        <v>1120.23</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>48.01</v>
+        <v>1120.66</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>47.82</v>
+        <v>1120.66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>RHETAN</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>23.14</v>
+        <v>450.43</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>23.07</v>
+        <v>438.52</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>26.68</v>
+        <v>453.55</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>26.69</v>
+        <v>452.6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>RKSWAMY</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>93.98</v>
+        <v>78.72</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>91.15000000000001</v>
+        <v>77.66</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>93.66</v>
+        <v>83.14</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>93.11</v>
+        <v>83.14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>RUBYMILLS</t>
+          <t>MAMATA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>427.71</v>
+        <v>419.02</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>397.02</v>
+        <v>404.21</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>457</v>
+        <v>419.4</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>450</v>
+        <v>418.9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>MANAKSIA</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>44.82</v>
+        <v>63.83</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>43.14</v>
+        <v>60.38</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>46.87</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>46.91</v>
+        <v>66.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>SBILIQETF</t>
+          <t>MANORAMA</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>1054.54</v>
+        <v>2002.66</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1054.52</v>
+        <v>1924.68</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>1054.91</v>
+        <v>2093.3</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>1054.92</v>
+        <v>2085.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>SHREEJISPG</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>673.1</v>
+        <v>542.45</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>647.8</v>
+        <v>516.96</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>699.8</v>
+        <v>546.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>700</v>
+        <v>548.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>SPECTRUM</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>2293.16</v>
+        <v>272.48</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>2170.44</v>
+        <v>272.48</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>2486.8</v>
+        <v>299.69</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>2486.8</v>
+        <v>299.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>SUDEEPPHRM</t>
+          <t>MENNPIS</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>1317.3</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>1252.22</v>
+        <v>75.48999999999999</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>1323.3</v>
+        <v>80.43000000000001</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>1323.5</v>
+        <v>80.48</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>4637.28</v>
+        <v>435.51</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>4553.14</v>
+        <v>423.42</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>4708.3</v>
+        <v>463.8</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>4700</v>
+        <v>463.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>SUPRIYA</t>
+          <t>MMP</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>860.48</v>
+        <v>427.19</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>826.41</v>
+        <v>399.29</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>909.1</v>
+        <v>460.25</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>913</v>
+        <v>466</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>TBZ</t>
+          <t>MTARTECH</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>452.74</v>
+        <v>7292</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>415.87</v>
+        <v>6963.3</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>528.9</v>
+        <v>7501</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>528.9</v>
+        <v>7501</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>UNIVPHOTO</t>
+          <t>MVELECTRO</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>473.47</v>
+        <v>840.8200000000001</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>457.91</v>
+        <v>758.37</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>514.9</v>
+        <v>917.5</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>514.9</v>
+        <v>912</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>VALIANTORG</t>
+          <t>MVGJL</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>314.83</v>
+        <v>194.53</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>302.1</v>
+        <v>174.7</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>326.1</v>
+        <v>214.64</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>329</v>
+        <v>215</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>VIJIFIN</t>
+          <t>MYSORPETRO</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>16.27</v>
+        <v>134.93</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>16.27</v>
+        <v>128.81</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>16.91</v>
+        <v>147.09</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>16.91</v>
+        <v>147.09</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>VINDHYATEL</t>
+          <t>NECCLTD</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>2803.7</v>
+        <v>18.46</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>2627.48</v>
+        <v>17.65</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>2765</v>
+        <v>19.59</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>2778</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>WHIRLPOOL</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>813.75</v>
+        <v>2217.9</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>794.88</v>
+        <v>2138.72</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>815.35</v>
+        <v>2255.2</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>814</v>
+        <v>2247.7</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>WINDLAS</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,45 +1943,973 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1121.65</v>
+        <v>74.75</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>1067.83</v>
+        <v>70.69</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1154.75</v>
+        <v>79.92</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>1152</v>
+        <v>79.98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>PARSVNATH</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>1.66</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>PENIND</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>173.81</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>168.43</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>178.08</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>177.74</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>PFOCUS</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>305.46</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>291.81</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>316.3</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>316.3</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>PKTEA</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>889.63</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>772.61</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1136.3</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>PPL</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>269.04</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>259.52</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>287.75</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>RBLBANK</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>411.82</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>399.98</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>416</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>REDINGTON</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>377.29</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>363.91</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>378.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>RKSWAMY</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>94.59999999999999</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>91.75</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>93.04000000000001</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>ROLLT</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>RPGLIFE</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>2754.44</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>2643.82</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>2812</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>2796.1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>RSL</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>185.83</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>180.91</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>190.09</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>190.95</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>SBC</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>44.2</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>48.68</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>SBILIQETF</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1054.74</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>1054.72</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1055.16</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>1055.16</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>SHANTIGEAR</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>629.26</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>586.04</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>707.75</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>SHREEJISPG</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>685.79</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>660.29</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>713.1</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>714.9</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>SIKKO</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>5.62</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>SOLARINDS</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>21755</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>21093</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>22355</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>22355</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>SPECTRUM</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>2406.5</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>2274.64</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>2741.6</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>2741.6</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>SPLPETRO</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>775.47</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>747.39</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>813.55</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>STLNETWORK</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>29.77</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>28.36</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>33.2</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>STLTECH</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>771.1</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>739.35</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>865.9</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>865.9</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>STYRENIX</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>2080.8</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>2022.22</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>2146.5</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>2154</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>SUNDARMFIN</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>4673.4</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>4577.86</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>4728</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>4722.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>SUNSHINE</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>484.38</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>453.55</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>481.2</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>SUPRIYA</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>883.6799999999999</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>847.13</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>911.4</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>878.96</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>845.6</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>876.35</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>876.3</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>UNIMECH</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1533.9</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>1474.22</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1586.4</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>UNIVPHOTO</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>498.07</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>476.51</v>
+      </c>
+      <c r="F79" s="3" t="n">
+        <v>566.25</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>VALIANTORG</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>327.95</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>314.42</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>359.5</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>359.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>VSTL</t>
+        </is>
+      </c>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>119.37</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>115.1</v>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>123.41</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>123.5</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>WHEELS</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>1854.04</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>1709.26</v>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>2400.6</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>2450</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
           <t>WOCKPHARMA</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>2025.06</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>1923</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>2208</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>2212.8</v>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>2102.08</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>1995.54</v>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>2248.8</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>2240</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>XCHANGING</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>U  ▲ UpTrend</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>62.69</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>60.63</v>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>63.28</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>64.73</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AAREYDRUGS</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>96.98</v>
+        <v>1075.82</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>93.70999999999999</v>
+        <v>1075.8</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>99.98</v>
+        <v>1076.19</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>99.20999999999999</v>
+        <v>1076.19</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AIRAN</t>
+          <t>ARTEMISMED</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>16.06</v>
+        <v>345.24</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>15.29</v>
+        <v>329.47</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>17.66</v>
+        <v>348.55</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>17.6</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ALLCARGO</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>12.76</v>
+        <v>371.96</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>12.16</v>
+        <v>356.45</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12.75</v>
+        <v>379.1</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>12.86</v>
+        <v>379.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ALMONDZ</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>18.74</v>
+        <v>341.78</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>17.73</v>
+        <v>324.02</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>19</v>
+        <v>351.5</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>19.07</v>
+        <v>351.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>AMANTA</t>
+          <t>DJML</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,22 +638,22 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>195.61</v>
+        <v>78.95</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>194.91</v>
+        <v>73.5</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>205.89</v>
+        <v>81.75</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>205.89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>DSKULKARNI</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1075.62</v>
+        <v>19.5</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1075.59</v>
+        <v>19.5</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1076.06</v>
+        <v>20.59</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1076.06</v>
+        <v>20.59</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>APOLLO</t>
+          <t>EIEL</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>401.43</v>
+        <v>206.83</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>388.81</v>
+        <v>199.71</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>422.45</v>
+        <v>211.65</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>420.5</v>
+        <v>211.9</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>AXISCADES</t>
+          <t>GESHIP</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1791.4</v>
+        <v>1391.3</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1713.52</v>
+        <v>1355.86</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1875.7</v>
+        <v>1400.2</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1882.8</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BANCOINDIA</t>
+          <t>GOACARBON</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>630.42</v>
+        <v>418.3</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>616.92</v>
+        <v>388.92</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>635.15</v>
+        <v>440.25</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>634.1</v>
+        <v>435</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>BGRENERGY</t>
+          <t>GPTHEALTH</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>251.52</v>
+        <v>160.75</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>236.85</v>
+        <v>155.9</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>248.87</v>
+        <v>161.29</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>248.4</v>
+        <v>161.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>CENTUM</t>
+          <t>INDORAMA</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>4012.76</v>
+        <v>80.58</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3746.9</v>
+        <v>72.69</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>4250.5</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>4225.5</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>DEEDEV</t>
+          <t>JUBLPHARMA</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>676.52</v>
+        <v>969.13</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>642.54</v>
+        <v>941.47</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>674.75</v>
+        <v>1025.65</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>670</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>DEEPINDS</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>774.34</v>
+        <v>0.06</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>730.9</v>
+        <v>0.06</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>792.7</v>
+        <v>0.08</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>794.7</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>DENTA</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>281.8</v>
+        <v>36.34</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>271.2</v>
+        <v>33.74</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>283.2</v>
+        <v>40.93</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>283.55</v>
+        <v>41.14</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>DSKULKARNI</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>19.05</v>
+        <v>1143.73</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>19.05</v>
+        <v>1143.63</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>19.8</v>
+        <v>1144.03</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>19.8</v>
+        <v>1144.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>202.48</v>
+        <v>1097.78</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>195.51</v>
+        <v>1097.76</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>206.06</v>
+        <v>1098.14</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>204.3</v>
+        <v>1098.13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GENESYS</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>245.34</v>
+        <v>115.82</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>231.45</v>
+        <v>115.8</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>274.31</v>
+        <v>115.84</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>272.06</v>
+        <v>115.85</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1371.52</v>
+        <v>1120.44</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1337.86</v>
+        <v>1120.42</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1393.4</v>
+        <v>1120.8</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1391.5</v>
+        <v>1120.81</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>GMMPFAUDLR</t>
+          <t>LYKALABS</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1193.36</v>
+        <v>80.61</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1123.78</v>
+        <v>79.7</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1305.4</v>
+        <v>84.2</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>1305</v>
+        <v>84.2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>MANAKSIA</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>396.1</v>
+        <v>66.77</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>374.79</v>
+        <v>62.55</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>463.5</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>463.5</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>INDIAGLYCO</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>263.86</v>
+        <v>549.46</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>259.48</v>
+        <v>527.45</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>301.3</v>
+        <v>559.75</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>301.3</v>
+        <v>559.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>76.58</v>
+        <v>286.1</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>69.44</v>
+        <v>286.1</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>86.13</v>
+        <v>314.67</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>85</v>
+        <v>314.67</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>JASH</t>
+          <t>MEDICAMEQ</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>495.79</v>
+        <v>296.4</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>478.63</v>
+        <v>273.41</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>518.75</v>
+        <v>307.5</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>519.15</v>
+        <v>302</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>JINDRILL</t>
+          <t>MIDHANI</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>672.53</v>
+        <v>447.79</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>643.46</v>
+        <v>433.07</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>673.75</v>
+        <v>463.35</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>672.5</v>
+        <v>464.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>KILITCH</t>
+          <t>MYSORPETRO</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>181.05</v>
+        <v>140.61</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>173.89</v>
+        <v>134.61</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>188.45</v>
+        <v>148.52</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>187</v>
+        <v>148.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>KISSHT</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>318.68</v>
+        <v>2264.64</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>303.36</v>
+        <v>2162.3</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>322.85</v>
+        <v>2388.9</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>324</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>KSHINTL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>1081.29</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1027.03</v>
+        <v>73.41</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1152.05</v>
+        <v>83.05</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1149</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.06</v>
+        <v>1.61</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.06</v>
+        <v>1.61</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.08</v>
+        <v>1.69</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.08</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>1143.51</v>
+        <v>974.4299999999999</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1143.42</v>
+        <v>847.09</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1143.91</v>
+        <v>1094.2</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1143.9</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>PPL</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>1097.58</v>
+        <v>276.31</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1097.56</v>
+        <v>264.72</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1098.02</v>
+        <v>290.9</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>1098.02</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>RAJOOENG</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>115.8</v>
+        <v>53.72</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>115.78</v>
+        <v>50.97</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>115.83</v>
+        <v>54.89</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>115.84</v>
+        <v>54.94</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDPLUS</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,22 +1421,22 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>1102.14</v>
+        <v>384.6</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1101.89</v>
+        <v>371.23</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1102.39</v>
+        <v>392</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>1102.39</v>
+        <v>395</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>SANATHAN</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1450,22 +1450,22 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1120.25</v>
+        <v>474.32</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1120.23</v>
+        <v>455.12</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>1120.66</v>
+        <v>483.1</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>1120.66</v>
+        <v>486.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -1479,22 +1479,22 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>450.43</v>
+        <v>61.21</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>438.52</v>
+        <v>60.75</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>453.55</v>
+        <v>64.39</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>452.6</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>SBC</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -1508,22 +1508,22 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>78.72</v>
+        <v>47.36</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>77.66</v>
+        <v>45.4</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>83.14</v>
+        <v>48.05</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>83.14</v>
+        <v>48.09</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>MAMATA</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -1537,22 +1537,22 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>419.02</v>
+        <v>1054.93</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>404.21</v>
+        <v>1054.91</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>419.4</v>
+        <v>1055.27</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>418.9</v>
+        <v>1055.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA</t>
+          <t>SHANTIGEAR</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -1566,22 +1566,22 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>63.83</v>
+        <v>670.86</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>60.38</v>
+        <v>619.86</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>66.20999999999999</v>
+        <v>725.45</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>66.06</v>
+        <v>733</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>MANORAMA</t>
+          <t>SHREEJISPG</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -1595,22 +1595,22 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>2002.66</v>
+        <v>699.15</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1924.68</v>
+        <v>674.09</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>2093.3</v>
+        <v>713.1</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>2085.2</v>
+        <v>713</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>SIKKO</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
@@ -1624,22 +1624,22 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>542.45</v>
+        <v>5.55</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>516.96</v>
+        <v>5.25</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>546.1</v>
+        <v>5.56</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>548.4</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>SPECTRUM</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -1653,22 +1653,22 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>272.48</v>
+        <v>2546.22</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>272.48</v>
+        <v>2435.8</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>299.69</v>
+        <v>2878.6</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>299.69</v>
+        <v>2878.6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>MENNPIS</t>
+          <t>SPLPETRO</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -1682,22 +1682,22 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>799.38</v>
       </c>
       <c r="E42" s="3" t="n">
-        <v>75.48999999999999</v>
+        <v>766.74</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>80.43000000000001</v>
+        <v>828.15</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>80.48</v>
+        <v>830</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>SREEL</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -1711,22 +1711,22 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>435.51</v>
+        <v>312.42</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>423.42</v>
+        <v>282.4</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>463.8</v>
+        <v>370.3</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>463.7</v>
+        <v>367.5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>MMP</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -1740,22 +1740,22 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>427.19</v>
+        <v>31.1</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>399.29</v>
+        <v>29.75</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>460.25</v>
+        <v>34.86</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>466</v>
+        <v>34.86</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>MTARTECH</t>
+          <t>STLTECH</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
@@ -1769,22 +1769,22 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>7292</v>
+        <v>805.48</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>6963.3</v>
+        <v>774.25</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>7501</v>
+        <v>854.75</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>7501</v>
+        <v>858</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>MVELECTRO</t>
+          <t>STYRENIX</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -1798,22 +1798,22 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>840.8200000000001</v>
+        <v>2107.2</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>758.37</v>
+        <v>2052.82</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>917.5</v>
+        <v>2142.9</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>912</v>
+        <v>2135</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>MVGJL</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -1827,22 +1827,22 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>194.53</v>
+        <v>4700.42</v>
       </c>
       <c r="E47" s="3" t="n">
-        <v>174.7</v>
+        <v>4603.12</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>214.64</v>
+        <v>4703</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>215</v>
+        <v>4693.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO</t>
+          <t>SUNSHINE</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
@@ -1856,22 +1856,22 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>134.93</v>
+        <v>497.25</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>128.81</v>
+        <v>463.28</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>147.09</v>
+        <v>509.7</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>147.09</v>
+        <v>511</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>NECCLTD</t>
+          <t>SUPRIYA</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
@@ -1885,22 +1885,22 @@
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>18.46</v>
+        <v>900.41</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>17.65</v>
+        <v>867.6900000000001</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>19.59</v>
+        <v>917.45</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>19.4</v>
+        <v>919.4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>TAMBOLIIN</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
@@ -1914,22 +1914,22 @@
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2217.9</v>
+        <v>274.45</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2138.72</v>
+        <v>262.17</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2255.2</v>
+        <v>299.95</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>2247.7</v>
+        <v>299.95</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>TEXMOPIPES</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>74.75</v>
+        <v>53.87</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>70.69</v>
+        <v>48.98</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>79.92</v>
+        <v>56.44</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>79.98</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>UDAYJEW</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -1972,22 +1972,22 @@
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1.58</v>
+        <v>169.65</v>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1.58</v>
+        <v>156.39</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1.66</v>
+        <v>175.12</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>1.66</v>
+        <v>175</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>PENIND</t>
+          <t>UNIVPHOTO</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2001,22 +2001,22 @@
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>173.81</v>
+        <v>524.0700000000001</v>
       </c>
       <c r="E53" s="3" t="n">
-        <v>168.43</v>
+        <v>496.52</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>178.08</v>
+        <v>540.5</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>177.74</v>
+        <v>540.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>PFOCUS</t>
+          <t>WHEELS</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2030,22 +2030,22 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>305.46</v>
+        <v>2040.66</v>
       </c>
       <c r="E54" s="3" t="n">
-        <v>291.81</v>
+        <v>1839.84</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>316.3</v>
+        <v>2313</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>316.3</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>XTRANET</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
@@ -2059,857 +2059,16 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>889.63</v>
+        <v>281.1</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>772.61</v>
+        <v>247.41</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>1136.3</v>
+        <v>285.59</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>PPL</t>
-        </is>
-      </c>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="n">
-        <v>269.04</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>259.52</v>
-      </c>
-      <c r="F56" s="3" t="n">
-        <v>287.55</v>
-      </c>
-      <c r="G56" s="3" t="n">
-        <v>287.75</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>RBLBANK</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="n">
-        <v>411.82</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>399.98</v>
-      </c>
-      <c r="F57" s="3" t="n">
-        <v>416</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>REDINGTON</t>
-        </is>
-      </c>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="n">
-        <v>377.29</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>363.91</v>
-      </c>
-      <c r="F58" s="3" t="n">
-        <v>378.05</v>
-      </c>
-      <c r="G58" s="3" t="n">
-        <v>378.5</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>RKSWAMY</t>
-        </is>
-      </c>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="n">
-        <v>94.59999999999999</v>
-      </c>
-      <c r="E59" s="3" t="n">
-        <v>91.75</v>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>93.04000000000001</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>ROLLT</t>
-        </is>
-      </c>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="F60" s="3" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>4.75</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>RPGLIFE</t>
-        </is>
-      </c>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="n">
-        <v>2754.44</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>2643.82</v>
-      </c>
-      <c r="F61" s="3" t="n">
-        <v>2812</v>
-      </c>
-      <c r="G61" s="3" t="n">
-        <v>2796.1</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>RSL</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="n">
-        <v>185.83</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>180.91</v>
-      </c>
-      <c r="F62" s="3" t="n">
-        <v>190.09</v>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>190.95</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>44.2</v>
-      </c>
-      <c r="F63" s="3" t="n">
-        <v>48.68</v>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>48.7</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="n">
-        <v>1054.74</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>1054.72</v>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>1055.16</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>1055.16</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>SHANTIGEAR</t>
-        </is>
-      </c>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="n">
-        <v>629.26</v>
-      </c>
-      <c r="E65" s="3" t="n">
-        <v>586.04</v>
-      </c>
-      <c r="F65" s="3" t="n">
-        <v>707.75</v>
-      </c>
-      <c r="G65" s="3" t="n">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>SHREEJISPG</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="n">
-        <v>685.79</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>660.29</v>
-      </c>
-      <c r="F66" s="3" t="n">
-        <v>713.1</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>714.9</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>SIKKO</t>
-        </is>
-      </c>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>5.58</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>5.62</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>SOLARINDS</t>
-        </is>
-      </c>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="n">
-        <v>21755</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>21093</v>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>22355</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>22355</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>SPECTRUM</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="n">
-        <v>2406.5</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>2274.64</v>
-      </c>
-      <c r="F69" s="3" t="n">
-        <v>2741.6</v>
-      </c>
-      <c r="G69" s="3" t="n">
-        <v>2741.6</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>SPLPETRO</t>
-        </is>
-      </c>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="n">
-        <v>775.47</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>747.39</v>
-      </c>
-      <c r="F70" s="3" t="n">
-        <v>813.55</v>
-      </c>
-      <c r="G70" s="3" t="n">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK</t>
-        </is>
-      </c>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="n">
-        <v>29.77</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>28.36</v>
-      </c>
-      <c r="F71" s="3" t="n">
-        <v>33.2</v>
-      </c>
-      <c r="G71" s="3" t="n">
-        <v>33.2</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="n">
-        <v>771.1</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>739.35</v>
-      </c>
-      <c r="F72" s="3" t="n">
-        <v>865.9</v>
-      </c>
-      <c r="G72" s="3" t="n">
-        <v>865.9</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>STYRENIX</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="n">
-        <v>2080.8</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>2022.22</v>
-      </c>
-      <c r="F73" s="3" t="n">
-        <v>2146.5</v>
-      </c>
-      <c r="G73" s="3" t="n">
-        <v>2154</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>SUNDARMFIN</t>
-        </is>
-      </c>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="n">
-        <v>4673.4</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>4577.86</v>
-      </c>
-      <c r="F74" s="3" t="n">
-        <v>4728</v>
-      </c>
-      <c r="G74" s="3" t="n">
-        <v>4722.1</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>SUNSHINE</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="n">
-        <v>484.38</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>453.55</v>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>481.2</v>
-      </c>
-      <c r="G75" s="3" t="n">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>SUPRIYA</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="n">
-        <v>883.6799999999999</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>847.13</v>
-      </c>
-      <c r="F76" s="3" t="n">
-        <v>911.4</v>
-      </c>
-      <c r="G76" s="3" t="n">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TITAGARH</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="n">
-        <v>878.96</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>845.6</v>
-      </c>
-      <c r="F77" s="3" t="n">
-        <v>876.35</v>
-      </c>
-      <c r="G77" s="3" t="n">
-        <v>876.3</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>UNIMECH</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="n">
-        <v>1533.9</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>1474.22</v>
-      </c>
-      <c r="F78" s="3" t="n">
-        <v>1586.4</v>
-      </c>
-      <c r="G78" s="3" t="n">
-        <v>1587</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>UNIVPHOTO</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="n">
-        <v>498.07</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>476.51</v>
-      </c>
-      <c r="F79" s="3" t="n">
-        <v>566.25</v>
-      </c>
-      <c r="G79" s="3" t="n">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>VALIANTORG</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="n">
-        <v>327.95</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>314.42</v>
-      </c>
-      <c r="F80" s="3" t="n">
-        <v>359.5</v>
-      </c>
-      <c r="G80" s="3" t="n">
-        <v>359.5</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>VSTL</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="n">
-        <v>119.37</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>123.41</v>
-      </c>
-      <c r="G81" s="3" t="n">
-        <v>123.5</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>WHEELS</t>
-        </is>
-      </c>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="n">
-        <v>1854.04</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>1709.26</v>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>2400.6</v>
-      </c>
-      <c r="G82" s="3" t="n">
-        <v>2450</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>WOCKPHARMA</t>
-        </is>
-      </c>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="n">
-        <v>2102.08</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>1995.54</v>
-      </c>
-      <c r="F83" s="3" t="n">
-        <v>2248.8</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>2240</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>XCHANGING</t>
-        </is>
-      </c>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="n">
-        <v>62.69</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>60.63</v>
-      </c>
-      <c r="F84" s="3" t="n">
-        <v>63.28</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>64.73</v>
+        <v>280.3</v>
       </c>
     </row>
   </sheetData>

--- a/data/uptrend_5day.xlsx
+++ b/data/uptrend_5day.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G55"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -508,7 +508,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AONELIQUID</t>
+          <t>ANMOL</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -522,22 +522,22 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>1075.82</v>
+        <v>13.55</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>1075.8</v>
+        <v>11.66</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1076.19</v>
+        <v>16.87</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1076.19</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ARTEMISMED</t>
+          <t>AONELIQUID</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -551,22 +551,22 @@
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>345.24</v>
+        <v>1076.11</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>329.47</v>
+        <v>1076.08</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>348.55</v>
+        <v>1076.74</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>347</v>
+        <v>1076.74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>CRIZAC</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -580,22 +580,22 @@
         </is>
       </c>
       <c r="D4" s="3" t="n">
-        <v>371.96</v>
+        <v>175.01</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>356.45</v>
+        <v>167.54</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>379.1</v>
+        <v>186.68</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>379.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>DIACABS</t>
+          <t>DEEP</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -609,22 +609,22 @@
         </is>
       </c>
       <c r="D5" s="3" t="n">
-        <v>341.78</v>
+        <v>40.42</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>324.02</v>
+        <v>36.41</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>351.5</v>
+        <v>46.08</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>351.5</v>
+        <v>45.51</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>DJML</t>
+          <t>DIACABS</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -638,16 +638,16 @@
         </is>
       </c>
       <c r="D6" s="3" t="n">
-        <v>78.95</v>
+        <v>347.99</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>73.5</v>
+        <v>329.02</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>81.75</v>
+        <v>369.05</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>83</v>
+        <v>369.05</v>
       </c>
     </row>
     <row r="7">
@@ -667,22 +667,22 @@
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>19.5</v>
+        <v>19.97</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>19.5</v>
+        <v>19.97</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>20.59</v>
+        <v>21</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>20.59</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EIEL</t>
+          <t>EMPOWER</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -696,22 +696,22 @@
         </is>
       </c>
       <c r="D8" s="3" t="n">
-        <v>206.83</v>
+        <v>2.09</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>199.71</v>
+        <v>2.01</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>211.65</v>
+        <v>2.28</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>211.9</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GESHIP</t>
+          <t>INVPRECQ</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1391.3</v>
+        <v>1341.88</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>1355.86</v>
+        <v>1340.48</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1400.2</v>
+        <v>1405.8</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>1403</v>
+        <v>1405.8</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>GOACARBON</t>
+          <t>KABRAEXTRU</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -754,22 +754,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>418.3</v>
+        <v>670.98</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>388.92</v>
+        <v>625.8200000000001</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>440.25</v>
+        <v>723.15</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>435</v>
+        <v>725</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>GPTHEALTH</t>
+          <t>KESORAMIND</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
@@ -783,22 +783,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>160.75</v>
+        <v>11.5</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>155.9</v>
+        <v>11.47</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>161.29</v>
+        <v>12.01</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>161.06</v>
+        <v>12.01</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>INDORAMA</t>
+          <t>KSHITIJ-RE</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -812,22 +812,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>80.58</v>
+        <v>0.06</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>72.69</v>
+        <v>0.06</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>82.93000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>83.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>JUBLPHARMA</t>
+          <t>KSR</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -841,22 +841,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>969.13</v>
+        <v>38.57</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>941.47</v>
+        <v>35.9</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1025.65</v>
+        <v>42.4</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>1026</v>
+        <v>42.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>KSHITIJ-RE</t>
+          <t>LIQUIDADD</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -870,22 +870,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.06</v>
+        <v>1144.02</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.06</v>
+        <v>1143.92</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.08</v>
+        <v>1144.6</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.08</v>
+        <v>1144.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>KSR</t>
+          <t>LIQUIDBETF</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -899,22 +899,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>36.34</v>
+        <v>1098.06</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>33.74</v>
+        <v>1097.94</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>40.93</v>
+        <v>1098.68</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>41.14</v>
+        <v>1098.68</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDADD</t>
+          <t>LIQUIDCASE</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -928,22 +928,22 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1143.73</v>
+        <v>115.85</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1143.63</v>
+        <v>115.83</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1144.03</v>
+        <v>115.91</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>1144.04</v>
+        <v>115.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDBETF</t>
+          <t>LIQUIDSHRI</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -957,22 +957,22 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1097.78</v>
+        <v>1120.71</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>1097.76</v>
+        <v>1120.69</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1098.14</v>
+        <v>1121.3</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>1098.13</v>
+        <v>1121.3</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDCASE</t>
+          <t>MANAKSIA</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -986,22 +986,22 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>115.82</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>115.8</v>
+        <v>64.72</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>115.84</v>
+        <v>70.95</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>115.85</v>
+        <v>71.7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>LIQUIDSHRI</t>
+          <t>MAXESTATES</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1015,22 +1015,22 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1120.44</v>
+        <v>555.86</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1120.42</v>
+        <v>533</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1120.8</v>
+        <v>560.45</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>1120.81</v>
+        <v>559</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>LYKALABS</t>
+          <t>MBECL</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1044,22 +1044,22 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>80.61</v>
+        <v>300.4</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>79.7</v>
+        <v>300.4</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>84.2</v>
+        <v>330.4</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>84.2</v>
+        <v>330.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>MANAKSIA</t>
+          <t>NEOGEN</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>66.77</v>
+        <v>2312.84</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>62.55</v>
+        <v>2194.38</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>70.51000000000001</v>
+        <v>2373</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>70.40000000000001</v>
+        <v>2387.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>MAXESTATES</t>
+          <t>NRBBEARING</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1102,22 +1102,22 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>549.46</v>
+        <v>494.25</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>527.45</v>
+        <v>470.49</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>559.75</v>
+        <v>514.65</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>559.5</v>
+        <v>516.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>MBECL</t>
+          <t>PAISALO</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1131,22 +1131,22 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>286.1</v>
+        <v>80.56</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>286.1</v>
+        <v>76.36</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>314.67</v>
+        <v>84.23</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>314.67</v>
+        <v>83.98999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>MEDICAMEQ</t>
+          <t>PARSVNATH</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>296.4</v>
+        <v>1.65</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>273.41</v>
+        <v>1.65</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>307.5</v>
+        <v>1.72</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>302</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>MIDHANI</t>
+          <t>RAYMOND</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1189,22 +1189,22 @@
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>447.79</v>
+        <v>852.96</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>433.07</v>
+        <v>777.67</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>463.35</v>
+        <v>1002.8</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>464.3</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>MYSORPETRO</t>
+          <t>RCOM</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -1218,22 +1218,22 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>140.61</v>
+        <v>0.92</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>134.61</v>
+        <v>0.89</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>148.52</v>
+        <v>1.01</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>148.5</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>NEOGEN</t>
+          <t>SANGINITA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -1247,22 +1247,22 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2264.64</v>
+        <v>62.68</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>2162.3</v>
+        <v>62.68</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>2388.9</v>
+        <v>65.67</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2388</v>
+        <v>65.67</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>PAISALO</t>
+          <t>SBILIQETF</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1276,22 +1276,22 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>77.81999999999999</v>
+        <v>1055.21</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>73.41</v>
+        <v>1055.19</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>83.05</v>
+        <v>1055.8</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>82.7</v>
+        <v>1055.8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>PARSVNATH</t>
+          <t>SHEKHAWATI</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -1305,22 +1305,22 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>1.61</v>
+        <v>17.49</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.61</v>
+        <v>16.5</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.69</v>
+        <v>19.37</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>1.69</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>STLNETWORK</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -1334,22 +1334,22 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>974.4299999999999</v>
+        <v>32.77</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>847.09</v>
+        <v>31.44</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>1094.2</v>
+        <v>36.6</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1090</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PPL</t>
+          <t>SYSTMTXC</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -1363,22 +1363,22 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>276.31</v>
+        <v>67.37</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>264.72</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>290.9</v>
+        <v>72.53</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>291</v>
+        <v>72.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>RAJOOENG</t>
+          <t>TAMBOLIIN</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1392,22 +1392,22 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>53.72</v>
+        <v>285.43</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>50.97</v>
+        <v>273.73</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>54.89</v>
+        <v>306.85</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>54.94</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>TECHNOCRAF</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -1421,654 +1421,16 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>384.6</v>
+        <v>426.73</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>371.23</v>
+        <v>397.74</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>392</v>
+        <v>442.3</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>SANATHAN</t>
-        </is>
-      </c>
-      <c r="B34" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v>474.32</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>455.12</v>
-      </c>
-      <c r="F34" s="3" t="n">
-        <v>483.1</v>
-      </c>
-      <c r="G34" s="3" t="n">
-        <v>486.5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>SANGINITA</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v>61.21</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="F35" s="3" t="n">
-        <v>64.39</v>
-      </c>
-      <c r="G35" s="3" t="n">
-        <v>64.39</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>SBC</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v>47.36</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>45.4</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>48.05</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>48.09</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>SBILIQETF</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v>1054.93</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>1054.91</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>1055.27</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>1055.29</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>SHANTIGEAR</t>
-        </is>
-      </c>
-      <c r="B38" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v>670.86</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>619.86</v>
-      </c>
-      <c r="F38" s="3" t="n">
-        <v>725.45</v>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>SHREEJISPG</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v>699.15</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>674.09</v>
-      </c>
-      <c r="F39" s="3" t="n">
-        <v>713.1</v>
-      </c>
-      <c r="G39" s="3" t="n">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>SIKKO</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="F40" s="3" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="G40" s="3" t="n">
-        <v>5.61</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>SPECTRUM</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D41" s="3" t="n">
-        <v>2546.22</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>2435.8</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>2878.6</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>2878.6</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>SPLPETRO</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n">
-        <v>799.38</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>766.74</v>
-      </c>
-      <c r="F42" s="3" t="n">
-        <v>828.15</v>
-      </c>
-      <c r="G42" s="3" t="n">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>SREEL</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="n">
-        <v>312.42</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>282.4</v>
-      </c>
-      <c r="F43" s="3" t="n">
-        <v>370.3</v>
-      </c>
-      <c r="G43" s="3" t="n">
-        <v>367.5</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>STLNETWORK</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="n">
-        <v>31.1</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>29.75</v>
-      </c>
-      <c r="F44" s="3" t="n">
-        <v>34.86</v>
-      </c>
-      <c r="G44" s="3" t="n">
-        <v>34.86</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>STLTECH</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v>805.48</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>774.25</v>
-      </c>
-      <c r="F45" s="3" t="n">
-        <v>854.75</v>
-      </c>
-      <c r="G45" s="3" t="n">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>STYRENIX</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n">
-        <v>2107.2</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>2052.82</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>2142.9</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>SUNDARMFIN</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D47" s="3" t="n">
-        <v>4700.42</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>4603.12</v>
-      </c>
-      <c r="F47" s="3" t="n">
-        <v>4703</v>
-      </c>
-      <c r="G47" s="3" t="n">
-        <v>4693.9</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>SUNSHINE</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="n">
-        <v>497.25</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>463.28</v>
-      </c>
-      <c r="F48" s="3" t="n">
-        <v>509.7</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>SUPRIYA</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="n">
-        <v>900.41</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>867.6900000000001</v>
-      </c>
-      <c r="F49" s="3" t="n">
-        <v>917.45</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>919.4</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TAMBOLIIN</t>
-        </is>
-      </c>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="n">
-        <v>274.45</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>262.17</v>
-      </c>
-      <c r="F50" s="3" t="n">
-        <v>299.95</v>
-      </c>
-      <c r="G50" s="3" t="n">
-        <v>299.95</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TEXMOPIPES</t>
-        </is>
-      </c>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="n">
-        <v>53.87</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>48.98</v>
-      </c>
-      <c r="F51" s="3" t="n">
-        <v>56.44</v>
-      </c>
-      <c r="G51" s="3" t="n">
-        <v>57.36</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>UDAYJEW</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="n">
-        <v>169.65</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>156.39</v>
-      </c>
-      <c r="F52" s="3" t="n">
-        <v>175.12</v>
-      </c>
-      <c r="G52" s="3" t="n">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>UNIVPHOTO</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="n">
-        <v>524.0700000000001</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>496.52</v>
-      </c>
-      <c r="F53" s="3" t="n">
-        <v>540.5</v>
-      </c>
-      <c r="G53" s="3" t="n">
-        <v>540.5</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>WHEELS</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="n">
-        <v>2040.66</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>1839.84</v>
-      </c>
-      <c r="F54" s="3" t="n">
-        <v>2313</v>
-      </c>
-      <c r="G54" s="3" t="n">
-        <v>2267</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>XTRANET</t>
-        </is>
-      </c>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>U  ▲ UpTrend</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="n">
-        <v>281.1</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>247.41</v>
-      </c>
-      <c r="F55" s="3" t="n">
-        <v>285.59</v>
-      </c>
-      <c r="G55" s="3" t="n">
-        <v>280.3</v>
+        <v>437.5</v>
       </c>
     </row>
   </sheetData>
